--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2018_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2018_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:12</t>
+    <t xml:space="preserve">2026-09-10 00:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2018_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2018_coquimbo.xlsx
@@ -36,6 +36,9 @@
     <t xml:space="preserve">Coquimbo</t>
   </si>
   <si>
+    <t xml:space="preserve">Paihuano</t>
+  </si>
+  <si>
     <t xml:space="preserve">Illapel</t>
   </si>
   <si>
@@ -75,9 +78,6 @@
     <t xml:space="preserve">Río Hurtado</t>
   </si>
   <si>
-    <t xml:space="preserve">Paihuano</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:16</t>
+    <t xml:space="preserve">2026-09-18 10:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -517,13 +517,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4201</v>
+        <v>4105</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>67.56</v>
+        <v>68.96</v>
       </c>
     </row>
     <row r="3">
@@ -534,13 +534,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4106</v>
+        <v>4201</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>64.17</v>
+        <v>67.56</v>
       </c>
     </row>
     <row r="4">
@@ -551,13 +551,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4204</v>
+        <v>4106</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>63.01</v>
+        <v>64.17</v>
       </c>
     </row>
     <row r="5">
@@ -565,16 +565,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4102</v>
+        <v>4204</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>62.78</v>
+        <v>63.01</v>
       </c>
     </row>
     <row r="6">
@@ -582,16 +582,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4301</v>
+        <v>4102</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>62.38</v>
+        <v>62.78</v>
       </c>
     </row>
     <row r="7">
@@ -602,13 +602,13 @@
         <v>10</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4103</v>
+        <v>4301</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>62.03</v>
+        <v>62.38</v>
       </c>
     </row>
     <row r="8">
@@ -619,13 +619,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4101</v>
+        <v>4103</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>61.62</v>
+        <v>62.03</v>
       </c>
     </row>
     <row r="9">
@@ -636,13 +636,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4203</v>
+        <v>4101</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>61.26</v>
+        <v>61.62</v>
       </c>
     </row>
     <row r="10">
@@ -653,13 +653,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4104</v>
+        <v>4203</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>58.41</v>
+        <v>61.26</v>
       </c>
     </row>
     <row r="11">
@@ -670,13 +670,13 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4302</v>
+        <v>4104</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>58.02</v>
+        <v>58.41</v>
       </c>
     </row>
     <row r="12">
@@ -687,13 +687,13 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4303</v>
+        <v>4302</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>57.53</v>
+        <v>58.02</v>
       </c>
     </row>
     <row r="13">
@@ -704,13 +704,13 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>4304</v>
+        <v>4303</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>56.75</v>
+        <v>57.53</v>
       </c>
     </row>
     <row r="14">
@@ -721,13 +721,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4202</v>
+        <v>4304</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>53.76</v>
+        <v>56.75</v>
       </c>
     </row>
     <row r="15">
@@ -738,13 +738,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4305</v>
+        <v>4202</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>50.58</v>
+        <v>53.76</v>
       </c>
     </row>
     <row r="16">
@@ -755,10 +755,14 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4105</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+        <v>4305</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>50.58</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E16"/>
